--- a/05_Figures/F06_prediction/modules/training/comp_hypertrophy/plain/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/modules/training/comp_hypertrophy/plain/c_data/results.xlsx
@@ -548,7 +548,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-19.2855094683721</v>
@@ -556,10 +556,18 @@
       <c r="I3" t="n">
         <v>0.674725274725275</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.0995024875621891</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0845771144278607</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1319.39515252005</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1555.653298688</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -583,6 +591,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-221.095867577341</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-4948.30889890087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-98.6553662108494</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-3552.83303334698</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-2088.18076860829</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-74.721103138716</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-6.70535454624719</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-495.58220220495</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-170.003497907372</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-618.051496090371</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-81.1335585991798</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-2.00886050866146</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-870.449084200718</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-7.59318910592571</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-394.818362725589</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1849.24035154931</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-539.916518474112</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1886.67527733545</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-5983.97392535709</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-256.513345982523</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-658.192624376777</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-180.547153018158</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1218.54897832236</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-80.3861858632438</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-800.212219208422</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1459.98980030126</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-2.40355799206571</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.259795699017707</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-817.917888160646</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-104.749026012104</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-21.6653318652941</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-64.9002592938182</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1204.88403566133</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-385.217161481081</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-700.156339293101</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-424.149272298538</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-3448.67843734643</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-300.550226871456</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-354.536521548257</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1825.70859963389</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-490.683671678891</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-5018.89212933136</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-286.707136833351</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1875.80141315146</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1435.67771192566</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-3747.40545511775</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-7346.43137742109</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-131.934179383273</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-2336.66778217497</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-2116.27365494256</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-2516.97411290055</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-28.4745924710164</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-3862.77449519806</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1407.29023745973</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-38.5529864983818</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2162.76581102806</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1228.25171737641</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-4.21874435458412</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-583.928359579982</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-3290.77779089522</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1761.22924955924</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-98.6818776337591</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-3.36287709419862</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-2286.12607045116</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-4601.3363880143</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-564.236218812096</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-189.481459137882</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-3432.6589980419</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1610.55433126703</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-928.155692978245</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-8.53139767508692</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-871.29737932287</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-3042.52190841417</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1214.09251999718</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-16.0974425666443</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-228.295287383324</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-3517.77981156074</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-65.525958340911</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.8586126192637</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-3601.58136272279</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-6620.00980793187</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-795.455539655939</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-22.8794780936944</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-467.831116604549</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-188.589985243108</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-169.571481875523</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-270.487591273491</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1673.27144034207</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-622.526973192787</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-426.254884336137</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-148.836093779879</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-6.99324020581547</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-541.624619870208</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-549.977926516727</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-3438.3827430145</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-220.121960450125</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1979.90215544151</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-957.152006359441</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1480.06353270108</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-2058.77970935643</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-956.731806616582</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-3431.73062450336</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-7304.58357680569</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-4107.42767863372</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1225.36451316115</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-6.02178102283829</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1144.811600503</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-4457.49902804951</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-2941.9717213829</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1851.01594075439</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-3596.52416241483</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-605.334252574691</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-449.184497846094</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-4885.53974865483</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-4774.97324388183</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1152.8325291806</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1382.22700386676</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2758.24527029205</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-912.081654709442</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-505.290566252178</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-63.1769528536011</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-853.362243865545</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-147.632499879425</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-187.241707540287</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-735.049340168412</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-392.234860552009</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-459.64823457901</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-227.166762704449</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1180.68587780626</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-101.884264801177</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.40353537103496</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-695.649533478027</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-311.809041452372</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-2125.89940457126</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-2113.70150762135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-298.295076091832</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-2612.96032387506</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-458.216886532596</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1133.50478724242</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-166.606784369327</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-783.779922675007</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-1025.05509100351</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.88448507917513</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-4564.75586103193</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1836.7012307774</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-722.988031192435</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-399.781990726433</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-245.502212593729</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-88.8542895674176</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-2906.77927598718</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-480.974524109301</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1334.69277372764</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1361.6588821388</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-41.371004635061</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-896.907853019388</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-388.770575903917</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1444.96860246663</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-5.25084557511303</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.578056439348311</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-244.659825013887</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-262.579382807028</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-220.729231816737</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1721.95750278819</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-2240.83159313888</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-2222.18937452531</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1860.98585204537</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-2.04360950150171</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-947.656686501539</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-434.805201929592</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-3295.37130409867</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-117.140360711082</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-120.464172231368</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1744.31757678815</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-2814.72865493687</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1682.3987038569</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-5566.37661406278</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-347.388213518434</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-18.1142101387775</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-107.039006712943</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-59.9847008828601</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-407.698777914079</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-22.7123006357268</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1455.27131227304</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-836.663936591586</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-195.435285927196</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-115.585701070374</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1308.91462569694</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-214.709879489807</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-102.420944479433</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-4451.93675321049</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-354.936437447094</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-4515.73543481732</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1616.34761216787</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.186391483082976</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-194.429023428162</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-4854.69852043212</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-47.3229190659364</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-2841.5042866968</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1188.81100174676</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-3088.27473754146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
